--- a/02-Task/English/English_Word_Ratings_2_template.xlsx
+++ b/02-Task/English/English_Word_Ratings_2_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
   <si>
     <t xml:space="preserve">explanations</t>
   </si>
@@ -80,29 +80,10 @@
     <t xml:space="preserve">item_order</t>
   </si>
   <si>
+    <t xml:space="preserve">left100 right600</t>
+  </si>
+  <si>
     <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">general_instructions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">## Instructions
-In this section, you will be presented with a series of object words. For each word, please list as many possible uses as you can think of.
-Please keep in mind that a single object can have more than one use. For example, a ball can be thrown, bounced, kicked, or stepped on.
-On each page, put **one different use in each box**. Avoid listing the same use in different words.
-You will see five boxes first. If you can think of more uses, you can add up to five additional boxes, one at a time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">general_submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Begin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left100 right600</t>
   </si>
   <si>
     <t xml:space="preserve">w01_prompt</t>
@@ -233,6 +214,9 @@
   </si>
   <si>
     <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">submit</t>
   </si>
   <si>
     <t xml:space="preserve">w01_submit</t>
@@ -1095,17 +1079,19 @@
     </row>
     <row r="2">
       <c r="A2"/>
-      <c r="B2"/>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2"/>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
@@ -1120,22 +1106,30 @@
       <c r="R2"/>
       <c r="S2"/>
       <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
+      <c r="U2" t="s">
+        <v>26</v>
+      </c>
+      <c r="V2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3"/>
-      <c r="B3"/>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
       <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3"/>
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F3"/>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -1150,24 +1144,30 @@
       <c r="R3"/>
       <c r="S3"/>
       <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
+      <c r="U3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4"/>
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F4"/>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
@@ -1183,29 +1183,29 @@
       <c r="S4"/>
       <c r="T4"/>
       <c r="U4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5"/>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
@@ -1221,29 +1221,29 @@
       <c r="S5"/>
       <c r="T5"/>
       <c r="U5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6"/>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
@@ -1259,29 +1259,29 @@
       <c r="S6"/>
       <c r="T6"/>
       <c r="U6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7"/>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
@@ -1297,32 +1297,34 @@
       <c r="S7"/>
       <c r="T7"/>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D8"/>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F8"/>
       <c r="G8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8"/>
-      <c r="I8"/>
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8"/>
@@ -1335,29 +1337,31 @@
       <c r="S8"/>
       <c r="T8"/>
       <c r="U8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9"/>
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
@@ -1373,34 +1377,34 @@
       <c r="S9"/>
       <c r="T9"/>
       <c r="U9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10"/>
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
       <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10"/>
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
       <c r="G10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10"/>
@@ -1413,31 +1417,31 @@
       <c r="S10"/>
       <c r="T10"/>
       <c r="U10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
@@ -1453,31 +1457,31 @@
       <c r="S11"/>
       <c r="T11"/>
       <c r="U11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
@@ -1493,31 +1497,31 @@
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
@@ -1533,31 +1537,25 @@
       <c r="S13"/>
       <c r="T13"/>
       <c r="U13" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14"/>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
+      <c r="B14"/>
       <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D14"/>
       <c r="E14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F14"/>
       <c r="G14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
@@ -1573,31 +1571,27 @@
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D15"/>
       <c r="E15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F15"/>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
@@ -1613,25 +1607,29 @@
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="V15" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16"/>
-      <c r="B16"/>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
       <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16"/>
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F16"/>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
@@ -1647,27 +1645,29 @@
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="V16" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17"/>
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
       <c r="E17" t="s">
         <v>75</v>
       </c>
       <c r="F17"/>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
@@ -1683,29 +1683,29 @@
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F18"/>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
@@ -1721,29 +1721,29 @@
       <c r="S18"/>
       <c r="T18"/>
       <c r="U18" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F19"/>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
@@ -1759,29 +1759,29 @@
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F20"/>
       <c r="G20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
@@ -1797,32 +1797,34 @@
       <c r="S20"/>
       <c r="T20"/>
       <c r="U20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D21"/>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F21"/>
       <c r="G21" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21"/>
-      <c r="I21"/>
+        <v>47</v>
+      </c>
+      <c r="H21" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" t="s">
+        <v>49</v>
+      </c>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
@@ -1835,29 +1837,31 @@
       <c r="S21"/>
       <c r="T21"/>
       <c r="U21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22"/>
+        <v>80</v>
+      </c>
+      <c r="F22" t="s">
+        <v>81</v>
+      </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
@@ -1873,34 +1877,34 @@
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V22" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23"/>
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
+      </c>
       <c r="E23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23"/>
+        <v>82</v>
+      </c>
+      <c r="F23" t="s">
+        <v>81</v>
+      </c>
       <c r="G23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H23" t="s">
-        <v>53</v>
-      </c>
-      <c r="I23" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H23"/>
+      <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
@@ -1913,31 +1917,31 @@
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
@@ -1953,31 +1957,31 @@
       <c r="S24"/>
       <c r="T24"/>
       <c r="U24" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
@@ -1993,31 +1997,31 @@
       <c r="S25"/>
       <c r="T25"/>
       <c r="U25" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
@@ -2033,31 +2037,25 @@
       <c r="S26"/>
       <c r="T26"/>
       <c r="U26" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27"/>
-      <c r="B27" t="s">
-        <v>28</v>
-      </c>
+      <c r="B27"/>
       <c r="C27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D27"/>
       <c r="E27" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" t="s">
-        <v>85</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="F27"/>
       <c r="G27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
@@ -2073,31 +2071,27 @@
       <c r="S27"/>
       <c r="T27"/>
       <c r="U27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D28"/>
       <c r="E28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" t="s">
-        <v>85</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="F28"/>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
@@ -2113,25 +2107,29 @@
       <c r="S28"/>
       <c r="T28"/>
       <c r="U28" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="V28" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29"/>
-      <c r="B29"/>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
       <c r="C29" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29"/>
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>29</v>
+      </c>
       <c r="E29" t="s">
         <v>90</v>
       </c>
       <c r="F29"/>
       <c r="G29" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
@@ -2147,27 +2145,29 @@
       <c r="S29"/>
       <c r="T29"/>
       <c r="U29" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="V29" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30"/>
+        <v>28</v>
+      </c>
+      <c r="D30" t="s">
+        <v>29</v>
+      </c>
       <c r="E30" t="s">
         <v>91</v>
       </c>
       <c r="F30"/>
       <c r="G30" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
@@ -2183,29 +2183,29 @@
       <c r="S30"/>
       <c r="T30"/>
       <c r="U30" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V30" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F31"/>
       <c r="G31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
@@ -2221,29 +2221,29 @@
       <c r="S31"/>
       <c r="T31"/>
       <c r="U31" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F32"/>
       <c r="G32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
@@ -2259,29 +2259,29 @@
       <c r="S32"/>
       <c r="T32"/>
       <c r="U32" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F33"/>
       <c r="G33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
@@ -2297,32 +2297,34 @@
       <c r="S33"/>
       <c r="T33"/>
       <c r="U33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D34"/>
       <c r="E34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F34"/>
       <c r="G34" t="s">
-        <v>45</v>
-      </c>
-      <c r="H34"/>
-      <c r="I34"/>
+        <v>47</v>
+      </c>
+      <c r="H34" t="s">
+        <v>48</v>
+      </c>
+      <c r="I34" t="s">
+        <v>49</v>
+      </c>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34"/>
@@ -2335,29 +2337,31 @@
       <c r="S34"/>
       <c r="T34"/>
       <c r="U34" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V34" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
-      </c>
-      <c r="F35"/>
+        <v>96</v>
+      </c>
+      <c r="F35" t="s">
+        <v>97</v>
+      </c>
       <c r="G35" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
@@ -2373,34 +2377,34 @@
       <c r="S35"/>
       <c r="T35"/>
       <c r="U35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V35" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36"/>
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
+        <v>29</v>
+      </c>
       <c r="E36" t="s">
-        <v>99</v>
-      </c>
-      <c r="F36"/>
+        <v>98</v>
+      </c>
+      <c r="F36" t="s">
+        <v>97</v>
+      </c>
       <c r="G36" t="s">
-        <v>52</v>
-      </c>
-      <c r="H36" t="s">
-        <v>53</v>
-      </c>
-      <c r="I36" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H36"/>
+      <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36"/>
@@ -2413,31 +2417,31 @@
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
@@ -2453,31 +2457,31 @@
       <c r="S37"/>
       <c r="T37"/>
       <c r="U37" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
@@ -2493,31 +2497,31 @@
       <c r="S38"/>
       <c r="T38"/>
       <c r="U38" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
@@ -2533,31 +2537,25 @@
       <c r="S39"/>
       <c r="T39"/>
       <c r="U39" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40"/>
-      <c r="B40" t="s">
-        <v>28</v>
-      </c>
+      <c r="B40"/>
       <c r="C40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D40" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D40"/>
       <c r="E40" t="s">
-        <v>104</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="F40"/>
       <c r="G40" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
@@ -2573,31 +2571,27 @@
       <c r="S40"/>
       <c r="T40"/>
       <c r="U40" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V40" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
-      </c>
-      <c r="D41" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D41"/>
       <c r="E41" t="s">
-        <v>105</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="F41"/>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
@@ -2613,25 +2607,29 @@
       <c r="S41"/>
       <c r="T41"/>
       <c r="U41" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="V41" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42"/>
-      <c r="B42"/>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
       <c r="C42" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42"/>
+        <v>28</v>
+      </c>
+      <c r="D42" t="s">
+        <v>29</v>
+      </c>
       <c r="E42" t="s">
         <v>106</v>
       </c>
       <c r="F42"/>
       <c r="G42" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H42"/>
       <c r="I42"/>
@@ -2647,27 +2645,29 @@
       <c r="S42"/>
       <c r="T42"/>
       <c r="U42" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="V42" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43"/>
+        <v>28</v>
+      </c>
+      <c r="D43" t="s">
+        <v>29</v>
+      </c>
       <c r="E43" t="s">
         <v>107</v>
       </c>
       <c r="F43"/>
       <c r="G43" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
@@ -2683,29 +2683,29 @@
       <c r="S43"/>
       <c r="T43"/>
       <c r="U43" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V43" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F44"/>
       <c r="G44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
@@ -2721,29 +2721,29 @@
       <c r="S44"/>
       <c r="T44"/>
       <c r="U44" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F45"/>
       <c r="G45" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
@@ -2759,29 +2759,29 @@
       <c r="S45"/>
       <c r="T45"/>
       <c r="U45" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F46"/>
       <c r="G46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H46"/>
       <c r="I46"/>
@@ -2797,32 +2797,34 @@
       <c r="S46"/>
       <c r="T46"/>
       <c r="U46" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>33</v>
-      </c>
-      <c r="D47" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D47"/>
       <c r="E47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F47"/>
       <c r="G47" t="s">
-        <v>45</v>
-      </c>
-      <c r="H47"/>
-      <c r="I47"/>
+        <v>47</v>
+      </c>
+      <c r="H47" t="s">
+        <v>48</v>
+      </c>
+      <c r="I47" t="s">
+        <v>49</v>
+      </c>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47"/>
@@ -2835,29 +2837,31 @@
       <c r="S47"/>
       <c r="T47"/>
       <c r="U47" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V47" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>114</v>
-      </c>
-      <c r="F48"/>
+        <v>112</v>
+      </c>
+      <c r="F48" t="s">
+        <v>113</v>
+      </c>
       <c r="G48" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H48"/>
       <c r="I48"/>
@@ -2873,34 +2877,34 @@
       <c r="S48"/>
       <c r="T48"/>
       <c r="U48" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V48" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49"/>
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
+      </c>
       <c r="E49" t="s">
-        <v>115</v>
-      </c>
-      <c r="F49"/>
+        <v>114</v>
+      </c>
+      <c r="F49" t="s">
+        <v>113</v>
+      </c>
       <c r="G49" t="s">
-        <v>52</v>
-      </c>
-      <c r="H49" t="s">
-        <v>53</v>
-      </c>
-      <c r="I49" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H49"/>
+      <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49"/>
@@ -2913,31 +2917,31 @@
       <c r="S49"/>
       <c r="T49"/>
       <c r="U49" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V49" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F50" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H50"/>
       <c r="I50"/>
@@ -2953,31 +2957,31 @@
       <c r="S50"/>
       <c r="T50"/>
       <c r="U50" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D51" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F51" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H51"/>
       <c r="I51"/>
@@ -2993,31 +2997,31 @@
       <c r="S51"/>
       <c r="T51"/>
       <c r="U51" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F52" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G52" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H52"/>
       <c r="I52"/>
@@ -3033,31 +3037,25 @@
       <c r="S52"/>
       <c r="T52"/>
       <c r="U52" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V52" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53"/>
-      <c r="B53" t="s">
-        <v>28</v>
-      </c>
+      <c r="B53"/>
       <c r="C53" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D53"/>
       <c r="E53" t="s">
-        <v>120</v>
-      </c>
-      <c r="F53" t="s">
-        <v>117</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="F53"/>
       <c r="G53" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H53"/>
       <c r="I53"/>
@@ -3073,31 +3071,27 @@
       <c r="S53"/>
       <c r="T53"/>
       <c r="U53" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V53" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D54"/>
       <c r="E54" t="s">
-        <v>121</v>
-      </c>
-      <c r="F54" t="s">
-        <v>117</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="F54"/>
       <c r="G54" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H54"/>
       <c r="I54"/>
@@ -3113,25 +3107,29 @@
       <c r="S54"/>
       <c r="T54"/>
       <c r="U54" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="V54" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
       <c r="A55"/>
-      <c r="B55"/>
+      <c r="B55" t="s">
+        <v>22</v>
+      </c>
       <c r="C55" t="s">
-        <v>25</v>
-      </c>
-      <c r="D55"/>
+        <v>28</v>
+      </c>
+      <c r="D55" t="s">
+        <v>29</v>
+      </c>
       <c r="E55" t="s">
         <v>122</v>
       </c>
       <c r="F55"/>
       <c r="G55" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H55"/>
       <c r="I55"/>
@@ -3147,27 +3145,29 @@
       <c r="S55"/>
       <c r="T55"/>
       <c r="U55" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="V55" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56"/>
+        <v>28</v>
+      </c>
+      <c r="D56" t="s">
+        <v>29</v>
+      </c>
       <c r="E56" t="s">
         <v>123</v>
       </c>
       <c r="F56"/>
       <c r="G56" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="H56"/>
       <c r="I56"/>
@@ -3183,29 +3183,29 @@
       <c r="S56"/>
       <c r="T56"/>
       <c r="U56" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V56" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E57" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F57"/>
       <c r="G57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H57"/>
       <c r="I57"/>
@@ -3221,29 +3221,29 @@
       <c r="S57"/>
       <c r="T57"/>
       <c r="U57" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F58"/>
       <c r="G58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H58"/>
       <c r="I58"/>
@@ -3259,29 +3259,29 @@
       <c r="S58"/>
       <c r="T58"/>
       <c r="U58" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C59" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E59" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F59"/>
       <c r="G59" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H59"/>
       <c r="I59"/>
@@ -3297,32 +3297,34 @@
       <c r="S59"/>
       <c r="T59"/>
       <c r="U59" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V59" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C60" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D60"/>
       <c r="E60" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F60"/>
       <c r="G60" t="s">
-        <v>45</v>
-      </c>
-      <c r="H60"/>
-      <c r="I60"/>
+        <v>47</v>
+      </c>
+      <c r="H60" t="s">
+        <v>48</v>
+      </c>
+      <c r="I60" t="s">
+        <v>49</v>
+      </c>
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60"/>
@@ -3335,29 +3337,31 @@
       <c r="S60"/>
       <c r="T60"/>
       <c r="U60" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V60" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E61" t="s">
-        <v>130</v>
-      </c>
-      <c r="F61"/>
+        <v>128</v>
+      </c>
+      <c r="F61" t="s">
+        <v>129</v>
+      </c>
       <c r="G61" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H61"/>
       <c r="I61"/>
@@ -3373,34 +3377,34 @@
       <c r="S61"/>
       <c r="T61"/>
       <c r="U61" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V61" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
-      </c>
-      <c r="D62"/>
+        <v>28</v>
+      </c>
+      <c r="D62" t="s">
+        <v>29</v>
+      </c>
       <c r="E62" t="s">
-        <v>131</v>
-      </c>
-      <c r="F62"/>
+        <v>130</v>
+      </c>
+      <c r="F62" t="s">
+        <v>129</v>
+      </c>
       <c r="G62" t="s">
-        <v>52</v>
-      </c>
-      <c r="H62" t="s">
-        <v>53</v>
-      </c>
-      <c r="I62" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H62"/>
+      <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62"/>
@@ -3413,31 +3417,31 @@
       <c r="S62"/>
       <c r="T62"/>
       <c r="U62" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V62" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D63" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H63"/>
       <c r="I63"/>
@@ -3453,31 +3457,31 @@
       <c r="S63"/>
       <c r="T63"/>
       <c r="U63" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C64" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F64" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H64"/>
       <c r="I64"/>
@@ -3493,31 +3497,31 @@
       <c r="S64"/>
       <c r="T64"/>
       <c r="U64" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F65" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G65" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H65"/>
       <c r="I65"/>
@@ -3533,31 +3537,25 @@
       <c r="S65"/>
       <c r="T65"/>
       <c r="U65" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66">
       <c r="A66"/>
-      <c r="B66" t="s">
-        <v>28</v>
-      </c>
+      <c r="B66"/>
       <c r="C66" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D66"/>
       <c r="E66" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" t="s">
-        <v>133</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="F66"/>
       <c r="G66" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H66"/>
       <c r="I66"/>
@@ -3573,31 +3571,27 @@
       <c r="S66"/>
       <c r="T66"/>
       <c r="U66" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="V66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>33</v>
-      </c>
-      <c r="D67" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D67"/>
       <c r="E67" t="s">
-        <v>137</v>
-      </c>
-      <c r="F67" t="s">
-        <v>133</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="F67"/>
       <c r="G67" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H67"/>
       <c r="I67"/>
@@ -3613,25 +3607,29 @@
       <c r="S67"/>
       <c r="T67"/>
       <c r="U67" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="V67" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68"/>
-      <c r="B68"/>
+      <c r="B68" t="s">
+        <v>22</v>
+      </c>
       <c r="C68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D68"/>
+        <v>28</v>
+      </c>
+      <c r="D68" t="s">
+        <v>29</v>
+      </c>
       <c r="E68" t="s">
         <v>138</v>
       </c>
       <c r="F68"/>
       <c r="G68" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H68"/>
       <c r="I68"/>
@@ -3647,27 +3645,29 @@
       <c r="S68"/>
       <c r="T68"/>
       <c r="U68" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="V68" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D69"/>
+        <v>28</v>
+      </c>
+      <c r="D69" t="s">
+        <v>29</v>
+      </c>
       <c r="E69" t="s">
         <v>139</v>
       </c>
       <c r="F69"/>
       <c r="G69" t="s">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="H69"/>
       <c r="I69"/>
@@ -3683,29 +3683,29 @@
       <c r="S69"/>
       <c r="T69"/>
       <c r="U69" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V69" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D70" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E70" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F70"/>
       <c r="G70" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H70"/>
       <c r="I70"/>
@@ -3721,29 +3721,29 @@
       <c r="S70"/>
       <c r="T70"/>
       <c r="U70" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C71" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E71" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F71"/>
       <c r="G71" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H71"/>
       <c r="I71"/>
@@ -3759,29 +3759,29 @@
       <c r="S71"/>
       <c r="T71"/>
       <c r="U71" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V71" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C72" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E72" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F72"/>
       <c r="G72" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H72"/>
       <c r="I72"/>
@@ -3797,32 +3797,34 @@
       <c r="S72"/>
       <c r="T72"/>
       <c r="U72" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>33</v>
-      </c>
-      <c r="D73" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D73"/>
       <c r="E73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F73"/>
       <c r="G73" t="s">
-        <v>45</v>
-      </c>
-      <c r="H73"/>
-      <c r="I73"/>
+        <v>47</v>
+      </c>
+      <c r="H73" t="s">
+        <v>48</v>
+      </c>
+      <c r="I73" t="s">
+        <v>49</v>
+      </c>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73"/>
@@ -3835,29 +3837,31 @@
       <c r="S73"/>
       <c r="T73"/>
       <c r="U73" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V73" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C74" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E74" t="s">
-        <v>146</v>
-      </c>
-      <c r="F74"/>
+        <v>144</v>
+      </c>
+      <c r="F74" t="s">
+        <v>145</v>
+      </c>
       <c r="G74" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H74"/>
       <c r="I74"/>
@@ -3873,34 +3877,34 @@
       <c r="S74"/>
       <c r="T74"/>
       <c r="U74" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V74" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75"/>
+        <v>28</v>
+      </c>
+      <c r="D75" t="s">
+        <v>29</v>
+      </c>
       <c r="E75" t="s">
-        <v>147</v>
-      </c>
-      <c r="F75"/>
+        <v>146</v>
+      </c>
+      <c r="F75" t="s">
+        <v>145</v>
+      </c>
       <c r="G75" t="s">
-        <v>52</v>
-      </c>
-      <c r="H75" t="s">
-        <v>53</v>
-      </c>
-      <c r="I75" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H75"/>
+      <c r="I75"/>
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75"/>
@@ -3913,31 +3917,31 @@
       <c r="S75"/>
       <c r="T75"/>
       <c r="U75" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V75" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D76" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F76" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G76" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H76"/>
       <c r="I76"/>
@@ -3953,31 +3957,31 @@
       <c r="S76"/>
       <c r="T76"/>
       <c r="U76" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C77" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D77" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F77" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H77"/>
       <c r="I77"/>
@@ -3993,31 +3997,31 @@
       <c r="S77"/>
       <c r="T77"/>
       <c r="U77" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V77" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D78" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F78" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H78"/>
       <c r="I78"/>
@@ -4033,31 +4037,25 @@
       <c r="S78"/>
       <c r="T78"/>
       <c r="U78" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V78" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79">
       <c r="A79"/>
-      <c r="B79" t="s">
-        <v>28</v>
-      </c>
+      <c r="B79"/>
       <c r="C79" t="s">
-        <v>33</v>
-      </c>
-      <c r="D79" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D79"/>
       <c r="E79" t="s">
-        <v>152</v>
-      </c>
-      <c r="F79" t="s">
-        <v>149</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F79"/>
       <c r="G79" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H79"/>
       <c r="I79"/>
@@ -4073,31 +4071,27 @@
       <c r="S79"/>
       <c r="T79"/>
       <c r="U79" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="V79" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>33</v>
-      </c>
-      <c r="D80" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D80"/>
       <c r="E80" t="s">
-        <v>153</v>
-      </c>
-      <c r="F80" t="s">
-        <v>149</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="F80"/>
       <c r="G80" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="H80"/>
       <c r="I80"/>
@@ -4113,25 +4107,29 @@
       <c r="S80"/>
       <c r="T80"/>
       <c r="U80" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="V80" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81"/>
-      <c r="B81"/>
+      <c r="B81" t="s">
+        <v>22</v>
+      </c>
       <c r="C81" t="s">
-        <v>25</v>
-      </c>
-      <c r="D81"/>
+        <v>28</v>
+      </c>
+      <c r="D81" t="s">
+        <v>29</v>
+      </c>
       <c r="E81" t="s">
         <v>154</v>
       </c>
       <c r="F81"/>
       <c r="G81" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H81"/>
       <c r="I81"/>
@@ -4147,27 +4145,29 @@
       <c r="S81"/>
       <c r="T81"/>
       <c r="U81" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="V81" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82"/>
+        <v>28</v>
+      </c>
+      <c r="D82" t="s">
+        <v>29</v>
+      </c>
       <c r="E82" t="s">
         <v>155</v>
       </c>
       <c r="F82"/>
       <c r="G82" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="H82"/>
       <c r="I82"/>
@@ -4183,29 +4183,29 @@
       <c r="S82"/>
       <c r="T82"/>
       <c r="U82" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V82" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D83" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F83"/>
       <c r="G83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H83"/>
       <c r="I83"/>
@@ -4221,29 +4221,29 @@
       <c r="S83"/>
       <c r="T83"/>
       <c r="U83" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V83" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D84" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F84"/>
       <c r="G84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H84"/>
       <c r="I84"/>
@@ -4259,29 +4259,29 @@
       <c r="S84"/>
       <c r="T84"/>
       <c r="U84" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D85" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F85"/>
       <c r="G85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H85"/>
       <c r="I85"/>
@@ -4297,32 +4297,34 @@
       <c r="S85"/>
       <c r="T85"/>
       <c r="U85" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V85" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
-      </c>
-      <c r="D86" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D86"/>
       <c r="E86" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F86"/>
       <c r="G86" t="s">
-        <v>45</v>
-      </c>
-      <c r="H86"/>
-      <c r="I86"/>
+        <v>47</v>
+      </c>
+      <c r="H86" t="s">
+        <v>48</v>
+      </c>
+      <c r="I86" t="s">
+        <v>49</v>
+      </c>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86"/>
@@ -4335,29 +4337,31 @@
       <c r="S86"/>
       <c r="T86"/>
       <c r="U86" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V86" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D87" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>162</v>
-      </c>
-      <c r="F87"/>
+        <v>160</v>
+      </c>
+      <c r="F87" t="s">
+        <v>161</v>
+      </c>
       <c r="G87" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H87"/>
       <c r="I87"/>
@@ -4373,34 +4377,34 @@
       <c r="S87"/>
       <c r="T87"/>
       <c r="U87" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V87" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>50</v>
-      </c>
-      <c r="D88"/>
+        <v>28</v>
+      </c>
+      <c r="D88" t="s">
+        <v>29</v>
+      </c>
       <c r="E88" t="s">
-        <v>163</v>
-      </c>
-      <c r="F88"/>
+        <v>162</v>
+      </c>
+      <c r="F88" t="s">
+        <v>161</v>
+      </c>
       <c r="G88" t="s">
-        <v>52</v>
-      </c>
-      <c r="H88" t="s">
-        <v>53</v>
-      </c>
-      <c r="I88" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H88"/>
+      <c r="I88"/>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88"/>
@@ -4413,31 +4417,31 @@
       <c r="S88"/>
       <c r="T88"/>
       <c r="U88" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V88" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C89" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D89" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F89" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H89"/>
       <c r="I89"/>
@@ -4453,31 +4457,31 @@
       <c r="S89"/>
       <c r="T89"/>
       <c r="U89" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C90" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D90" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F90" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G90" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H90"/>
       <c r="I90"/>
@@ -4493,31 +4497,31 @@
       <c r="S90"/>
       <c r="T90"/>
       <c r="U90" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C91" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D91" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F91" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H91"/>
       <c r="I91"/>
@@ -4533,31 +4537,25 @@
       <c r="S91"/>
       <c r="T91"/>
       <c r="U91" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V91" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92">
       <c r="A92"/>
-      <c r="B92" t="s">
-        <v>28</v>
-      </c>
+      <c r="B92"/>
       <c r="C92" t="s">
-        <v>33</v>
-      </c>
-      <c r="D92" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D92"/>
       <c r="E92" t="s">
-        <v>168</v>
-      </c>
-      <c r="F92" t="s">
-        <v>165</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="F92"/>
       <c r="G92" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H92"/>
       <c r="I92"/>
@@ -4573,31 +4571,27 @@
       <c r="S92"/>
       <c r="T92"/>
       <c r="U92" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V92" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C93" t="s">
-        <v>33</v>
-      </c>
-      <c r="D93" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D93"/>
       <c r="E93" t="s">
-        <v>169</v>
-      </c>
-      <c r="F93" t="s">
-        <v>165</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="F93"/>
       <c r="G93" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="H93"/>
       <c r="I93"/>
@@ -4613,25 +4607,29 @@
       <c r="S93"/>
       <c r="T93"/>
       <c r="U93" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="V93" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94">
       <c r="A94"/>
-      <c r="B94"/>
+      <c r="B94" t="s">
+        <v>22</v>
+      </c>
       <c r="C94" t="s">
-        <v>25</v>
-      </c>
-      <c r="D94"/>
+        <v>28</v>
+      </c>
+      <c r="D94" t="s">
+        <v>29</v>
+      </c>
       <c r="E94" t="s">
         <v>170</v>
       </c>
       <c r="F94"/>
       <c r="G94" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H94"/>
       <c r="I94"/>
@@ -4647,27 +4645,29 @@
       <c r="S94"/>
       <c r="T94"/>
       <c r="U94" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="V94" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C95" t="s">
-        <v>22</v>
-      </c>
-      <c r="D95"/>
+        <v>28</v>
+      </c>
+      <c r="D95" t="s">
+        <v>29</v>
+      </c>
       <c r="E95" t="s">
         <v>171</v>
       </c>
       <c r="F95"/>
       <c r="G95" t="s">
-        <v>172</v>
+        <v>34</v>
       </c>
       <c r="H95"/>
       <c r="I95"/>
@@ -4683,29 +4683,29 @@
       <c r="S95"/>
       <c r="T95"/>
       <c r="U95" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V95" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C96" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D96" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F96"/>
       <c r="G96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H96"/>
       <c r="I96"/>
@@ -4721,29 +4721,29 @@
       <c r="S96"/>
       <c r="T96"/>
       <c r="U96" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V96" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F97"/>
       <c r="G97" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H97"/>
       <c r="I97"/>
@@ -4759,29 +4759,29 @@
       <c r="S97"/>
       <c r="T97"/>
       <c r="U97" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V97" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D98" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E98" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F98"/>
       <c r="G98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H98"/>
       <c r="I98"/>
@@ -4797,32 +4797,34 @@
       <c r="S98"/>
       <c r="T98"/>
       <c r="U98" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V98" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C99" t="s">
-        <v>33</v>
-      </c>
-      <c r="D99" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D99"/>
       <c r="E99" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F99"/>
       <c r="G99" t="s">
-        <v>45</v>
-      </c>
-      <c r="H99"/>
-      <c r="I99"/>
+        <v>47</v>
+      </c>
+      <c r="H99" t="s">
+        <v>48</v>
+      </c>
+      <c r="I99" t="s">
+        <v>49</v>
+      </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99"/>
@@ -4835,29 +4837,31 @@
       <c r="S99"/>
       <c r="T99"/>
       <c r="U99" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V99" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D100" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E100" t="s">
-        <v>178</v>
-      </c>
-      <c r="F100"/>
+        <v>176</v>
+      </c>
+      <c r="F100" t="s">
+        <v>177</v>
+      </c>
       <c r="G100" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H100"/>
       <c r="I100"/>
@@ -4873,34 +4877,34 @@
       <c r="S100"/>
       <c r="T100"/>
       <c r="U100" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V100" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>50</v>
-      </c>
-      <c r="D101"/>
+        <v>28</v>
+      </c>
+      <c r="D101" t="s">
+        <v>29</v>
+      </c>
       <c r="E101" t="s">
-        <v>179</v>
-      </c>
-      <c r="F101"/>
+        <v>178</v>
+      </c>
+      <c r="F101" t="s">
+        <v>177</v>
+      </c>
       <c r="G101" t="s">
-        <v>52</v>
-      </c>
-      <c r="H101" t="s">
-        <v>53</v>
-      </c>
-      <c r="I101" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H101"/>
+      <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101"/>
@@ -4913,31 +4917,31 @@
       <c r="S101"/>
       <c r="T101"/>
       <c r="U101" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V101" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D102" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F102" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G102" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H102"/>
       <c r="I102"/>
@@ -4953,31 +4957,31 @@
       <c r="S102"/>
       <c r="T102"/>
       <c r="U102" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D103" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E103" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F103" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G103" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H103"/>
       <c r="I103"/>
@@ -4993,31 +4997,31 @@
       <c r="S103"/>
       <c r="T103"/>
       <c r="U103" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V103" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D104" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E104" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F104" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H104"/>
       <c r="I104"/>
@@ -5033,31 +5037,25 @@
       <c r="S104"/>
       <c r="T104"/>
       <c r="U104" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V104" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105">
       <c r="A105"/>
-      <c r="B105" t="s">
-        <v>28</v>
-      </c>
+      <c r="B105"/>
       <c r="C105" t="s">
-        <v>33</v>
-      </c>
-      <c r="D105" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D105"/>
       <c r="E105" t="s">
-        <v>184</v>
-      </c>
-      <c r="F105" t="s">
-        <v>181</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="F105"/>
       <c r="G105" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H105"/>
       <c r="I105"/>
@@ -5073,31 +5071,27 @@
       <c r="S105"/>
       <c r="T105"/>
       <c r="U105" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="V105" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>33</v>
-      </c>
-      <c r="D106" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D106"/>
       <c r="E106" t="s">
-        <v>185</v>
-      </c>
-      <c r="F106" t="s">
-        <v>181</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="F106"/>
       <c r="G106" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="H106"/>
       <c r="I106"/>
@@ -5113,25 +5107,29 @@
       <c r="S106"/>
       <c r="T106"/>
       <c r="U106" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="V106" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107">
       <c r="A107"/>
-      <c r="B107"/>
+      <c r="B107" t="s">
+        <v>22</v>
+      </c>
       <c r="C107" t="s">
-        <v>25</v>
-      </c>
-      <c r="D107"/>
+        <v>28</v>
+      </c>
+      <c r="D107" t="s">
+        <v>29</v>
+      </c>
       <c r="E107" t="s">
         <v>186</v>
       </c>
       <c r="F107"/>
       <c r="G107" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H107"/>
       <c r="I107"/>
@@ -5147,27 +5145,29 @@
       <c r="S107"/>
       <c r="T107"/>
       <c r="U107" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="V107" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C108" t="s">
-        <v>22</v>
-      </c>
-      <c r="D108"/>
+        <v>28</v>
+      </c>
+      <c r="D108" t="s">
+        <v>29</v>
+      </c>
       <c r="E108" t="s">
         <v>187</v>
       </c>
       <c r="F108"/>
       <c r="G108" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="H108"/>
       <c r="I108"/>
@@ -5183,29 +5183,29 @@
       <c r="S108"/>
       <c r="T108"/>
       <c r="U108" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V108" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D109" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E109" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F109"/>
       <c r="G109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H109"/>
       <c r="I109"/>
@@ -5221,29 +5221,29 @@
       <c r="S109"/>
       <c r="T109"/>
       <c r="U109" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V109" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C110" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D110" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E110" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F110"/>
       <c r="G110" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H110"/>
       <c r="I110"/>
@@ -5259,29 +5259,29 @@
       <c r="S110"/>
       <c r="T110"/>
       <c r="U110" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V110" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C111" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D111" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E111" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F111"/>
       <c r="G111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H111"/>
       <c r="I111"/>
@@ -5297,32 +5297,34 @@
       <c r="S111"/>
       <c r="T111"/>
       <c r="U111" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>33</v>
-      </c>
-      <c r="D112" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D112"/>
       <c r="E112" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F112"/>
       <c r="G112" t="s">
-        <v>45</v>
-      </c>
-      <c r="H112"/>
-      <c r="I112"/>
+        <v>47</v>
+      </c>
+      <c r="H112" t="s">
+        <v>48</v>
+      </c>
+      <c r="I112" t="s">
+        <v>49</v>
+      </c>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112"/>
@@ -5335,29 +5337,31 @@
       <c r="S112"/>
       <c r="T112"/>
       <c r="U112" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V112" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113">
       <c r="A113"/>
       <c r="B113" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C113" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D113" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E113" t="s">
-        <v>194</v>
-      </c>
-      <c r="F113"/>
+        <v>192</v>
+      </c>
+      <c r="F113" t="s">
+        <v>193</v>
+      </c>
       <c r="G113" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H113"/>
       <c r="I113"/>
@@ -5373,34 +5377,34 @@
       <c r="S113"/>
       <c r="T113"/>
       <c r="U113" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V113" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="114">
       <c r="A114"/>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C114" t="s">
-        <v>50</v>
-      </c>
-      <c r="D114"/>
+        <v>28</v>
+      </c>
+      <c r="D114" t="s">
+        <v>29</v>
+      </c>
       <c r="E114" t="s">
-        <v>195</v>
-      </c>
-      <c r="F114"/>
+        <v>194</v>
+      </c>
+      <c r="F114" t="s">
+        <v>193</v>
+      </c>
       <c r="G114" t="s">
-        <v>52</v>
-      </c>
-      <c r="H114" t="s">
-        <v>53</v>
-      </c>
-      <c r="I114" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H114"/>
+      <c r="I114"/>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114"/>
@@ -5413,31 +5417,31 @@
       <c r="S114"/>
       <c r="T114"/>
       <c r="U114" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V114" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="115">
       <c r="A115"/>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C115" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D115" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E115" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F115" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G115" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H115"/>
       <c r="I115"/>
@@ -5453,31 +5457,31 @@
       <c r="S115"/>
       <c r="T115"/>
       <c r="U115" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V115" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116">
       <c r="A116"/>
       <c r="B116" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C116" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D116" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E116" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F116" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G116" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H116"/>
       <c r="I116"/>
@@ -5493,31 +5497,31 @@
       <c r="S116"/>
       <c r="T116"/>
       <c r="U116" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V116" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="117">
       <c r="A117"/>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C117" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D117" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E117" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F117" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G117" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H117"/>
       <c r="I117"/>
@@ -5533,31 +5537,25 @@
       <c r="S117"/>
       <c r="T117"/>
       <c r="U117" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V117" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118">
       <c r="A118"/>
-      <c r="B118" t="s">
-        <v>28</v>
-      </c>
+      <c r="B118"/>
       <c r="C118" t="s">
-        <v>33</v>
-      </c>
-      <c r="D118" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D118"/>
       <c r="E118" t="s">
-        <v>200</v>
-      </c>
-      <c r="F118" t="s">
-        <v>197</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="F118"/>
       <c r="G118" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H118"/>
       <c r="I118"/>
@@ -5573,31 +5571,27 @@
       <c r="S118"/>
       <c r="T118"/>
       <c r="U118" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V118" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C119" t="s">
-        <v>33</v>
-      </c>
-      <c r="D119" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D119"/>
       <c r="E119" t="s">
-        <v>201</v>
-      </c>
-      <c r="F119" t="s">
-        <v>197</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="F119"/>
       <c r="G119" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="H119"/>
       <c r="I119"/>
@@ -5613,25 +5607,29 @@
       <c r="S119"/>
       <c r="T119"/>
       <c r="U119" t="s">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="V119" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120">
       <c r="A120"/>
-      <c r="B120"/>
+      <c r="B120" t="s">
+        <v>22</v>
+      </c>
       <c r="C120" t="s">
-        <v>25</v>
-      </c>
-      <c r="D120"/>
+        <v>28</v>
+      </c>
+      <c r="D120" t="s">
+        <v>29</v>
+      </c>
       <c r="E120" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F120"/>
       <c r="G120" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H120"/>
       <c r="I120"/>
@@ -5647,27 +5645,29 @@
       <c r="S120"/>
       <c r="T120"/>
       <c r="U120" t="s">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="V120" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121">
       <c r="A121"/>
       <c r="B121" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C121" t="s">
-        <v>22</v>
-      </c>
-      <c r="D121"/>
+        <v>28</v>
+      </c>
+      <c r="D121" t="s">
+        <v>29</v>
+      </c>
       <c r="E121" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F121"/>
       <c r="G121" t="s">
-        <v>204</v>
+        <v>34</v>
       </c>
       <c r="H121"/>
       <c r="I121"/>
@@ -5683,29 +5683,29 @@
       <c r="S121"/>
       <c r="T121"/>
       <c r="U121" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V121" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122">
       <c r="A122"/>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C122" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D122" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E122" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F122"/>
       <c r="G122" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H122"/>
       <c r="I122"/>
@@ -5721,29 +5721,29 @@
       <c r="S122"/>
       <c r="T122"/>
       <c r="U122" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V122" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C123" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D123" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E123" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F123"/>
       <c r="G123" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H123"/>
       <c r="I123"/>
@@ -5759,29 +5759,29 @@
       <c r="S123"/>
       <c r="T123"/>
       <c r="U123" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V123" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C124" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D124" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E124" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F124"/>
       <c r="G124" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H124"/>
       <c r="I124"/>
@@ -5797,32 +5797,34 @@
       <c r="S124"/>
       <c r="T124"/>
       <c r="U124" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V124" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="125">
       <c r="A125"/>
       <c r="B125" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C125" t="s">
-        <v>33</v>
-      </c>
-      <c r="D125" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D125"/>
       <c r="E125" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F125"/>
       <c r="G125" t="s">
-        <v>45</v>
-      </c>
-      <c r="H125"/>
-      <c r="I125"/>
+        <v>47</v>
+      </c>
+      <c r="H125" t="s">
+        <v>48</v>
+      </c>
+      <c r="I125" t="s">
+        <v>49</v>
+      </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125"/>
@@ -5835,29 +5837,31 @@
       <c r="S125"/>
       <c r="T125"/>
       <c r="U125" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V125" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126">
       <c r="A126"/>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C126" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D126" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E126" t="s">
-        <v>209</v>
-      </c>
-      <c r="F126"/>
+        <v>207</v>
+      </c>
+      <c r="F126" t="s">
+        <v>208</v>
+      </c>
       <c r="G126" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H126"/>
       <c r="I126"/>
@@ -5873,34 +5877,34 @@
       <c r="S126"/>
       <c r="T126"/>
       <c r="U126" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V126" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="127">
       <c r="A127"/>
       <c r="B127" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C127" t="s">
-        <v>50</v>
-      </c>
-      <c r="D127"/>
+        <v>28</v>
+      </c>
+      <c r="D127" t="s">
+        <v>29</v>
+      </c>
       <c r="E127" t="s">
-        <v>210</v>
-      </c>
-      <c r="F127"/>
+        <v>209</v>
+      </c>
+      <c r="F127" t="s">
+        <v>208</v>
+      </c>
       <c r="G127" t="s">
-        <v>52</v>
-      </c>
-      <c r="H127" t="s">
-        <v>53</v>
-      </c>
-      <c r="I127" t="s">
-        <v>54</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H127"/>
+      <c r="I127"/>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127"/>
@@ -5913,31 +5917,31 @@
       <c r="S127"/>
       <c r="T127"/>
       <c r="U127" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V127" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="128">
       <c r="A128"/>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C128" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D128" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E128" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F128" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G128" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H128"/>
       <c r="I128"/>
@@ -5953,31 +5957,31 @@
       <c r="S128"/>
       <c r="T128"/>
       <c r="U128" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V128" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129">
       <c r="A129"/>
       <c r="B129" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C129" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D129" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E129" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F129" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G129" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H129"/>
       <c r="I129"/>
@@ -5993,31 +5997,31 @@
       <c r="S129"/>
       <c r="T129"/>
       <c r="U129" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V129" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="130">
       <c r="A130"/>
       <c r="B130" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C130" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D130" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E130" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F130" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G130" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H130"/>
       <c r="I130"/>
@@ -6033,31 +6037,25 @@
       <c r="S130"/>
       <c r="T130"/>
       <c r="U130" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V130" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="131">
       <c r="A131"/>
-      <c r="B131" t="s">
-        <v>28</v>
-      </c>
+      <c r="B131"/>
       <c r="C131" t="s">
-        <v>33</v>
-      </c>
-      <c r="D131" t="s">
-        <v>34</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D131"/>
       <c r="E131" t="s">
-        <v>215</v>
-      </c>
-      <c r="F131" t="s">
-        <v>212</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="F131"/>
       <c r="G131" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H131"/>
       <c r="I131"/>
@@ -6073,84 +6071,10 @@
       <c r="S131"/>
       <c r="T131"/>
       <c r="U131" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V131" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132"/>
-      <c r="B132" t="s">
-        <v>28</v>
-      </c>
-      <c r="C132" t="s">
-        <v>33</v>
-      </c>
-      <c r="D132" t="s">
-        <v>34</v>
-      </c>
-      <c r="E132" t="s">
-        <v>216</v>
-      </c>
-      <c r="F132" t="s">
-        <v>212</v>
-      </c>
-      <c r="G132" t="s">
         <v>70</v>
-      </c>
-      <c r="H132"/>
-      <c r="I132"/>
-      <c r="J132"/>
-      <c r="K132"/>
-      <c r="L132"/>
-      <c r="M132"/>
-      <c r="N132"/>
-      <c r="O132"/>
-      <c r="P132"/>
-      <c r="Q132"/>
-      <c r="R132"/>
-      <c r="S132"/>
-      <c r="T132"/>
-      <c r="U132" t="s">
-        <v>65</v>
-      </c>
-      <c r="V132" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133"/>
-      <c r="B133"/>
-      <c r="C133" t="s">
-        <v>25</v>
-      </c>
-      <c r="D133"/>
-      <c r="E133" t="s">
-        <v>217</v>
-      </c>
-      <c r="F133"/>
-      <c r="G133" t="s">
-        <v>73</v>
-      </c>
-      <c r="H133"/>
-      <c r="I133"/>
-      <c r="J133"/>
-      <c r="K133"/>
-      <c r="L133"/>
-      <c r="M133"/>
-      <c r="N133"/>
-      <c r="O133"/>
-      <c r="P133"/>
-      <c r="Q133"/>
-      <c r="R133"/>
-      <c r="S133"/>
-      <c r="T133"/>
-      <c r="U133" t="s">
-        <v>65</v>
-      </c>
-      <c r="V133" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
